--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_CONSERVATION.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_CONSERVATION.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.95" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -584,10 +585,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -641,7 +647,8 @@
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -691,7 +698,8 @@
       </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -737,7 +745,8 @@
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -783,7 +792,8 @@
       </c>
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:L7"/>
